--- a/从零开始学Slots/从零开始学Slots-14-数值篇-Hold&Spin.xlsx
+++ b/从零开始学Slots/从零开始学Slots-14-数值篇-Hold&Spin.xlsx
@@ -5733,6 +5733,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L119" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -6768,5 +6771,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:P87" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-14-数值篇-Hold&Spin.xlsx
+++ b/从零开始学Slots/从零开始学Slots-14-数值篇-Hold&Spin.xlsx
@@ -4656,12 +4656,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0.0000%"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -4839,7 +4840,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4974,6 +4975,14 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5865,11 +5874,11 @@
       <c r="A12" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="35" t="n">
         <f aca="false">BINOMDIST(A12,$B$6,$B$7,FALSE())</f>
         <v>0.463291230159753</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="35" t="n">
         <f aca="false">SUM($B$12:B12)</f>
         <v>0.463291230159753</v>
       </c>
@@ -5882,11 +5891,11 @@
       <c r="A13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="35" t="n">
         <f aca="false">BINOMDIST(A13,$B$6,$B$7,FALSE())</f>
         <v>0.365756234336647</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="35" t="n">
         <f aca="false">SUM($B$12:B13)</f>
         <v>0.8290474644964</v>
       </c>
@@ -5899,11 +5908,11 @@
       <c r="A14" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="35" t="n">
         <f aca="false">BINOMDIST(A14,$B$6,$B$7,FALSE())</f>
         <v>0.13475229686087</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="35" t="n">
         <f aca="false">SUM($B$12:B14)</f>
         <v>0.96379976135727</v>
       </c>
@@ -5916,11 +5925,11 @@
       <c r="A15" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="20" t="n">
+      <c r="B15" s="35" t="n">
         <f aca="false">BINOMDIST(A15,$B$6,$B$7,FALSE())</f>
         <v>0.0307329799858125</v>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="35" t="n">
         <f aca="false">SUM($B$12:B15)</f>
         <v>0.994532741343083</v>
       </c>
@@ -5933,11 +5942,11 @@
       <c r="A16" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="35" t="n">
         <f aca="false">BINOMDIST(A16,$B$6,$B$7,FALSE())</f>
         <v>0.00485257578723355</v>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="35" t="n">
         <f aca="false">SUM($B$12:B16)</f>
         <v>0.999385317130316</v>
       </c>
@@ -5950,11 +5959,11 @@
       <c r="A17" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="20" t="n">
+      <c r="B17" s="35" t="n">
         <f aca="false">BINOMDIST(A17,$B$6,$B$7,FALSE())</f>
         <v>0.000561877196416516</v>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="35" t="n">
         <f aca="false">SUM($B$12:B17)</f>
         <v>0.999947194326733</v>
       </c>
@@ -5967,11 +5976,11 @@
       <c r="A18" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="20" t="n">
+      <c r="B18" s="35" t="n">
         <f aca="false">BINOMDIST(A18,$B$6,$B$7,FALSE())</f>
         <v>4.92874733698699E-005</v>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="35" t="n">
         <f aca="false">SUM($B$12:B18)</f>
         <v>0.999996481800103</v>
       </c>
@@ -5984,11 +5993,11 @@
       <c r="A19" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="20" t="n">
+      <c r="B19" s="35" t="n">
         <f aca="false">BINOMDIST(A19,$B$6,$B$7,FALSE())</f>
         <v>3.33524255886337E-006</v>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="35" t="n">
         <f aca="false">SUM($B$12:B19)</f>
         <v>0.999999817042662</v>
       </c>
@@ -6095,23 +6104,23 @@
         <f aca="false">$B$6-A28</f>
         <v>15</v>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="35" t="n">
         <f aca="false">IF($B28&lt;0,0,BINOMDIST(0,$B28,$B$7,FALSE()))</f>
         <v>0.463291230159753</v>
       </c>
-      <c r="D28" s="20" t="n">
+      <c r="D28" s="35" t="n">
         <f aca="false">IF($B28&lt;1,0,BINOMDIST(1,$B28,$B$7,FALSE()))</f>
         <v>0.365756234336647</v>
       </c>
-      <c r="E28" s="20" t="n">
+      <c r="E28" s="35" t="n">
         <f aca="false">IF($B28&lt;2,0,BINOMDIST(2,$B28,$B$7,FALSE()))</f>
         <v>0.13475229686087</v>
       </c>
-      <c r="F28" s="20" t="n">
+      <c r="F28" s="35" t="n">
         <f aca="false">IF($B28&lt;3,0,BINOMDIST(3,$B28,$B$7,FALSE()))</f>
         <v>0.0307329799858125</v>
       </c>
-      <c r="G28" s="20" t="n">
+      <c r="G28" s="35" t="n">
         <f aca="false">IF($B28&lt;4,0,BINOMDIST(4,$B28,$B$7,FALSE()))</f>
         <v>0.00485257578723355</v>
       </c>
@@ -6128,23 +6137,23 @@
         <f aca="false">$B$6-A29</f>
         <v>10</v>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="35" t="n">
         <f aca="false">IF($B29&lt;0,0,BINOMDIST(0,$B29,$B$7,FALSE()))</f>
         <v>0.598736939238379</v>
       </c>
-      <c r="D29" s="20" t="n">
+      <c r="D29" s="35" t="n">
         <f aca="false">IF($B29&lt;1,0,BINOMDIST(1,$B29,$B$7,FALSE()))</f>
         <v>0.315124704862305</v>
       </c>
-      <c r="E29" s="20" t="n">
+      <c r="E29" s="35" t="n">
         <f aca="false">IF($B29&lt;2,0,BINOMDIST(2,$B29,$B$7,FALSE()))</f>
         <v>0.0746347985200195</v>
       </c>
-      <c r="F29" s="20" t="n">
+      <c r="F29" s="35" t="n">
         <f aca="false">IF($B29&lt;3,0,BINOMDIST(3,$B29,$B$7,FALSE()))</f>
         <v>0.0104750594414062</v>
       </c>
-      <c r="G29" s="20" t="n">
+      <c r="G29" s="35" t="n">
         <f aca="false">IF($B29&lt;4,0,BINOMDIST(4,$B29,$B$7,FALSE()))</f>
         <v>0.000964808106445312</v>
       </c>
@@ -6161,23 +6170,23 @@
         <f aca="false">$B$6-A30</f>
         <v>5</v>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C30" s="35" t="n">
         <f aca="false">IF($B30&lt;0,0,BINOMDIST(0,$B30,$B$7,FALSE()))</f>
         <v>0.7737809375</v>
       </c>
-      <c r="D30" s="20" t="n">
+      <c r="D30" s="35" t="n">
         <f aca="false">IF($B30&lt;1,0,BINOMDIST(1,$B30,$B$7,FALSE()))</f>
         <v>0.2036265625</v>
       </c>
-      <c r="E30" s="20" t="n">
+      <c r="E30" s="35" t="n">
         <f aca="false">IF($B30&lt;2,0,BINOMDIST(2,$B30,$B$7,FALSE()))</f>
         <v>0.021434375</v>
       </c>
-      <c r="F30" s="20" t="n">
+      <c r="F30" s="35" t="n">
         <f aca="false">IF($B30&lt;3,0,BINOMDIST(3,$B30,$B$7,FALSE()))</f>
         <v>0.001128125</v>
       </c>
-      <c r="G30" s="20" t="n">
+      <c r="G30" s="35" t="n">
         <f aca="false">IF($B30&lt;4,0,BINOMDIST(4,$B30,$B$7,FALSE()))</f>
         <v>2.96875E-005</v>
       </c>
@@ -6194,23 +6203,23 @@
         <f aca="false">$B$6-A31</f>
         <v>3</v>
       </c>
-      <c r="C31" s="20" t="n">
+      <c r="C31" s="35" t="n">
         <f aca="false">IF($B31&lt;0,0,BINOMDIST(0,$B31,$B$7,FALSE()))</f>
         <v>0.857375</v>
       </c>
-      <c r="D31" s="20" t="n">
+      <c r="D31" s="35" t="n">
         <f aca="false">IF($B31&lt;1,0,BINOMDIST(1,$B31,$B$7,FALSE()))</f>
         <v>0.135375</v>
       </c>
-      <c r="E31" s="20" t="n">
+      <c r="E31" s="35" t="n">
         <f aca="false">IF($B31&lt;2,0,BINOMDIST(2,$B31,$B$7,FALSE()))</f>
         <v>0.007125</v>
       </c>
-      <c r="F31" s="20" t="n">
+      <c r="F31" s="35" t="n">
         <f aca="false">IF($B31&lt;3,0,BINOMDIST(3,$B31,$B$7,FALSE()))</f>
         <v>0.000125</v>
       </c>
-      <c r="G31" s="20" t="n">
+      <c r="G31" s="35" t="n">
         <f aca="false">IF($B31&lt;4,0,BINOMDIST(4,$B31,$B$7,FALSE()))</f>
         <v>0</v>
       </c>
@@ -6227,23 +6236,23 @@
         <f aca="false">$B$6-A32</f>
         <v>1</v>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C32" s="35" t="n">
         <f aca="false">IF($B32&lt;0,0,BINOMDIST(0,$B32,$B$7,FALSE()))</f>
         <v>0.95</v>
       </c>
-      <c r="D32" s="20" t="n">
+      <c r="D32" s="35" t="n">
         <f aca="false">IF($B32&lt;1,0,BINOMDIST(1,$B32,$B$7,FALSE()))</f>
         <v>0.05</v>
       </c>
-      <c r="E32" s="20" t="n">
+      <c r="E32" s="35" t="n">
         <f aca="false">IF($B32&lt;2,0,BINOMDIST(2,$B32,$B$7,FALSE()))</f>
         <v>0</v>
       </c>
-      <c r="F32" s="20" t="n">
+      <c r="F32" s="35" t="n">
         <f aca="false">IF($B32&lt;3,0,BINOMDIST(3,$B32,$B$7,FALSE()))</f>
         <v>0</v>
       </c>
-      <c r="G32" s="20" t="n">
+      <c r="G32" s="35" t="n">
         <f aca="false">IF($B32&lt;4,0,BINOMDIST(4,$B32,$B$7,FALSE()))</f>
         <v>0</v>
       </c>
@@ -6260,23 +6269,23 @@
         <f aca="false">$B$6-A33</f>
         <v>0</v>
       </c>
-      <c r="C33" s="20" t="n">
+      <c r="C33" s="35" t="n">
         <f aca="false">IF($B33&lt;0,0,BINOMDIST(0,$B33,$B$7,FALSE()))</f>
         <v>1</v>
       </c>
-      <c r="D33" s="20" t="n">
+      <c r="D33" s="35" t="n">
         <f aca="false">IF($B33&lt;1,0,BINOMDIST(1,$B33,$B$7,FALSE()))</f>
         <v>0</v>
       </c>
-      <c r="E33" s="20" t="n">
+      <c r="E33" s="35" t="n">
         <f aca="false">IF($B33&lt;2,0,BINOMDIST(2,$B33,$B$7,FALSE()))</f>
         <v>0</v>
       </c>
-      <c r="F33" s="20" t="n">
+      <c r="F33" s="35" t="n">
         <f aca="false">IF($B33&lt;3,0,BINOMDIST(3,$B33,$B$7,FALSE()))</f>
         <v>0</v>
       </c>
-      <c r="G33" s="20" t="n">
+      <c r="G33" s="35" t="n">
         <f aca="false">IF($B33&lt;4,0,BINOMDIST(4,$B33,$B$7,FALSE()))</f>
         <v>0</v>
       </c>
